--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487117_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487117_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7223</v>
+        <v>4.7412</v>
       </c>
       <c r="E2" t="n">
-        <v>4.426</v>
+        <v>4.6857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2964</v>
+        <v>0.0554</v>
       </c>
       <c r="G2" t="n">
         <v>3.8992</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.3564</v>
+        <v>-2.3376</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3986</v>
+        <v>-1.1388</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9578</v>
+        <v>-1.1987</v>
       </c>
       <c r="V2" t="n">
         <v>1.0564</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8692</v>
+        <v>0.5688</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3548</v>
+        <v>-0.8962</v>
       </c>
       <c r="F3" t="n">
-        <v>1.224</v>
+        <v>1.465</v>
       </c>
       <c r="G3" t="n">
         <v>0.9752</v>
@@ -688,13 +688,13 @@
         <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5328</v>
+        <v>-1.8333</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2195</v>
+        <v>-0.3219</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.7523</v>
+        <v>-1.5114</v>
       </c>
       <c r="V3" t="n">
         <v>1.4268</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5774</v>
+        <v>0.5169</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1601</v>
+        <v>-0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7375</v>
+        <v>0.5768</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1845</v>
@@ -766,13 +766,13 @@
         <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8633</v>
+        <v>-0.9237</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2829</v>
+        <v>-0.1828</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5804</v>
+        <v>-0.741</v>
       </c>
       <c r="V4" t="n">
         <v>0.8531</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1722</v>
+        <v>-0.9235</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8371</v>
+        <v>-2.3991</v>
       </c>
       <c r="F5" t="n">
-        <v>0.665</v>
+        <v>1.4756</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5145</v>
+        <v>-0.9195</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4519</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.9664</v>
+        <v>-0.2799</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0018</v>
+        <v>-0.8798</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5844</v>
+        <v>-0.8798</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5127</v>
+        <v>-0.0397</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8675</v>
+        <v>0.2402</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3802</v>
+        <v>-0.2799</v>
       </c>
       <c r="P5" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.5441</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.9301</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.4741</v>
-      </c>
       <c r="S5" t="n">
-        <v>-2.1614</v>
+        <v>-0.583</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.805</v>
+        <v>-0.5542</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3564</v>
+        <v>-0.0288</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0403</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.211</v>
+        <v>-1.2188</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4992</v>
+        <v>-1.9372</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2882</v>
+        <v>0.7185</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9195</v>
+        <v>-0.5145</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6395999999999999</v>
+        <v>1.4519</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2799</v>
+        <v>-1.9664</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8798</v>
+        <v>-0.0018</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8798</v>
+        <v>0.5844</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0397</v>
+        <v>-0.5127</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2402</v>
+        <v>0.8675</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2799</v>
+        <v>-1.3802</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>3.4741</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-2.208</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6544</v>
+        <v>-0.9052</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2162</v>
+        <v>-1.3029</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.0403</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.9401</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9405</v>
+        <v>-1.8413</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9168</v>
+        <v>-2.657</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9764</v>
+        <v>0.8157</v>
       </c>
       <c r="G7" t="n">
         <v>2.0216</v>
@@ -1000,13 +1000,13 @@
         <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0708</v>
+        <v>-0.9717</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5803</v>
+        <v>-0.3206</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4905</v>
+        <v>-0.6511</v>
       </c>
       <c r="V7" t="n">
         <v>0.1969</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6701</v>
+        <v>-2.4699</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0453</v>
+        <v>-3.086</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3752</v>
+        <v>0.6161</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4025</v>
@@ -1078,13 +1078,13 @@
         <v>2.7021</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1264</v>
+        <v>-1.9261</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.85</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2764</v>
+        <v>-1.0355</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6854</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2505</v>
+        <v>-3.2306</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2989</v>
+        <v>-2.1988</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9516</v>
+        <v>-1.0319</v>
       </c>
       <c r="G9" t="n">
         <v>-1.374</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4628</v>
+        <v>-1.4429</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8778</v>
+        <v>-0.7776</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.585</v>
+        <v>-0.6653</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1857</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6372</v>
+        <v>-4.6114</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.5583</v>
+        <v>-6.3987</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9212</v>
+        <v>1.7873</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5529</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2314</v>
+        <v>-1.2056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9518</v>
+        <v>-0.7922</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2796</v>
+        <v>-0.4135</v>
       </c>
       <c r="V10" t="n">
         <v>0.6562</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8462</v>
+        <v>-5.7926</v>
       </c>
       <c r="E11" t="n">
         <v>-4.734</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1121</v>
+        <v>-1.0586</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0153</v>
@@ -1312,13 +1312,13 @@
         <v>3.2811</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2804</v>
+        <v>-2.2269</v>
       </c>
       <c r="T11" t="n">
         <v>-1.043</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2374</v>
+        <v>-1.1839</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6386</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.5588</v>
+        <v>-14.2612</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.9785</v>
+        <v>-19.6813</v>
       </c>
       <c r="F12" t="n">
-        <v>5.4202</v>
+        <v>5.4199</v>
       </c>
       <c r="G12" t="n">
         <v>-3.067200000000001</v>
@@ -1372,7 +1372,7 @@
         <v>-5.879700000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4615999999999999</v>
+        <v>-0.4616</v>
       </c>
       <c r="N12" t="n">
         <v>1.7661</v>
@@ -1390,13 +1390,13 @@
         <v>21.2308</v>
       </c>
       <c r="S12" t="n">
-        <v>-15.9562</v>
+        <v>-15.6588</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.2243</v>
+        <v>-6.926900000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.731999999999999</v>
+        <v>-8.732100000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3606</v>
@@ -1405,13 +1405,13 @@
         <v>6.2568</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.6173</v>
+        <v>-6.617299999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.622</v>
+        <v>6.005</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3359</v>
+        <v>0.4257</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2861</v>
+        <v>5.5793</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7595</v>
+        <v>5.0645</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3137</v>
+        <v>0.5568</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4459</v>
+        <v>4.5076</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3253</v>
+        <v>3.776</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7976</v>
+        <v>3.0518</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4343</v>
+        <v>1.2884</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2141</v>
+        <v>-0.1674</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6483</v>
+        <v>1.4559</v>
       </c>
       <c r="P13" t="n">
-        <v>0.772</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9301</v>
+        <v>-5.7902</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7021</v>
+        <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5958</v>
+        <v>2.0854</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9407</v>
+        <v>0.9684</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6551</v>
+        <v>1.117</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5054</v>
+        <v>2.1363</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5054</v>
+        <v>0.6647</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7674</v>
+        <v>5.7757</v>
       </c>
       <c r="E14" t="n">
-        <v>1.922</v>
+        <v>2.8233</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8453</v>
+        <v>2.9524</v>
       </c>
       <c r="G14" t="n">
         <v>-2.7045</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6795</v>
+        <v>1.6878</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0569</v>
+        <v>0.9581</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6226</v>
+        <v>0.7297</v>
       </c>
       <c r="V14" t="n">
         <v>5.4414</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6184</v>
+        <v>5.6472</v>
       </c>
       <c r="E15" t="n">
-        <v>0.649</v>
+        <v>1.2498</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9694</v>
+        <v>4.3974</v>
       </c>
       <c r="G15" t="n">
         <v>4.8013</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5083</v>
+        <v>1.5371</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0873</v>
+        <v>0.6881</v>
       </c>
       <c r="U15" t="n">
-        <v>0.421</v>
+        <v>0.849</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2702</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2012</v>
+        <v>4.1037</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5757</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7768</v>
+        <v>3.2685</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0645</v>
+        <v>1.7595</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5568</v>
+        <v>0.3137</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5076</v>
+        <v>1.4459</v>
       </c>
       <c r="J16" t="n">
-        <v>3.776</v>
+        <v>1.3253</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0518</v>
+        <v>0.7976</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2884</v>
+        <v>0.4343</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1674</v>
+        <v>-0.2141</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4559</v>
+        <v>0.6483</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.2811</v>
+        <v>0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.7902</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>2.7021</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2816</v>
+        <v>3.0775</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.033</v>
+        <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3146</v>
+        <v>1.6375</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1363</v>
+        <v>-1.5054</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4716</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6647</v>
+        <v>-1.5054</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6933</v>
+        <v>1.226</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6988</v>
+        <v>-1.2996</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3921</v>
+        <v>2.5256</v>
       </c>
       <c r="G17" t="n">
         <v>1.332</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0478</v>
+        <v>1.5804</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2586</v>
+        <v>0.6577</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7892</v>
+        <v>0.9227</v>
       </c>
       <c r="V17" t="n">
         <v>0.2436</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4171</v>
+        <v>0.2993</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.7893</v>
+        <v>-0.0369</v>
       </c>
       <c r="F18" t="n">
-        <v>4.2064</v>
+        <v>0.3362</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.6302</v>
+        <v>-1.1067</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.868</v>
+        <v>-0.1656</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2378</v>
+        <v>-0.9411</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.124</v>
+        <v>-0.6262</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.033</v>
+        <v>0.0414</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.091</v>
+        <v>-0.6676</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4938</v>
+        <v>-0.4805</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.835</v>
+        <v>-0.207</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3288</v>
+        <v>-0.2735</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.8951</v>
+        <v>0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.7902</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8951</v>
+        <v>0.772</v>
       </c>
       <c r="S18" t="n">
-        <v>6.0342</v>
+        <v>0.6339</v>
       </c>
       <c r="T18" t="n">
-        <v>4.6111</v>
+        <v>0.5893</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4231</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9083</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1724</v>
+        <v>0.0197</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1371</v>
+        <v>0.1338</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3094</v>
+        <v>-0.1141</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1067</v>
+        <v>-1.5918</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1656</v>
+        <v>-0.4522</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9411</v>
+        <v>-1.1396</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6262</v>
+        <v>-0.1568</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0414</v>
+        <v>1.0971</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6676</v>
+        <v>-1.2538</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4805</v>
+        <v>-1.435</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.207</v>
+        <v>-1.5493</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2735</v>
+        <v>0.1142</v>
       </c>
       <c r="P19" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S19" t="n">
-        <v>0.507</v>
+        <v>1.0939</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4891</v>
+        <v>0.2905</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0178</v>
+        <v>0.8034</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2195</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2195</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3631</v>
+        <v>-1.8398</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7675</v>
+        <v>-5.9924</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5956</v>
+        <v>4.1525</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5918</v>
+        <v>-3.6302</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4522</v>
+        <v>-3.868</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1396</v>
+        <v>0.2378</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1568</v>
+        <v>-4.124</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0971</v>
+        <v>-3.033</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2538</v>
+        <v>-1.091</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.435</v>
+        <v>0.4938</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5493</v>
+        <v>-0.835</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1142</v>
+        <v>1.3288</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7371</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-5.7902</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7371</v>
+        <v>2.8951</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2888</v>
+        <v>3.7772</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6107</v>
+        <v>2.408</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3219</v>
+        <v>1.3692</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2195</v>
+        <v>0.9083</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2195</v>
+        <v>-0.6055</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.617</v>
+        <v>-2.577</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7519</v>
+        <v>-1.9522</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8651</v>
+        <v>-0.6248</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7771</v>
@@ -2092,13 +2092,13 @@
         <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6148</v>
+        <v>1.6548</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9175</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6973</v>
+        <v>0.9376</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4897</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9529</v>
+        <v>-2.7659</v>
       </c>
       <c r="E22" t="n">
         <v>-1.6067</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3462</v>
+        <v>-1.1591</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0799</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0238</v>
+        <v>0.1633</v>
       </c>
       <c r="T22" t="n">
         <v>0.0145</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0383</v>
+        <v>0.1487</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8842</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.5588</v>
+        <v>15.8939</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4201</v>
+        <v>-5.42</v>
       </c>
       <c r="F23" t="n">
-        <v>19.9786</v>
+        <v>21.3139</v>
       </c>
       <c r="G23" t="n">
         <v>3.0671</v>
@@ -2221,7 +2221,7 @@
         <v>8.107599999999998</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4615999999999991</v>
+        <v>0.4615999999999996</v>
       </c>
       <c r="K23" t="n">
         <v>-1.7661</v>
@@ -2233,10 +2233,10 @@
         <v>2.6054</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.2746</v>
+        <v>-3.274599999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>5.879799999999999</v>
+        <v>5.8798</v>
       </c>
       <c r="P23" t="n">
         <v>-4.825099999999999</v>
@@ -2248,22 +2248,22 @@
         <v>16.4056</v>
       </c>
       <c r="S23" t="n">
-        <v>15.9564</v>
+        <v>17.2913</v>
       </c>
       <c r="T23" t="n">
-        <v>8.731999999999999</v>
+        <v>8.7318</v>
       </c>
       <c r="U23" t="n">
-        <v>7.224300000000001</v>
+        <v>8.5594</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3605999999999987</v>
+        <v>0.3606000000000005</v>
       </c>
       <c r="W23" t="n">
         <v>6.6174</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.256699999999999</v>
+        <v>-6.2567</v>
       </c>
     </row>
   </sheetData>
